--- a/generated/spreadsheet/householder-planning-application-hh.xlsx
+++ b/generated/spreadsheet/householder-planning-application-hh.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,75 +1067,67 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>New or altered vehicle access</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1139,7 +1135,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1158,7 +1154,7 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1166,7 +1162,7 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1185,20 +1181,24 @@
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1208,23 +1208,27 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1239,27 +1243,23 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1283,14 +1283,18 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1300,7 +1304,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1319,18 +1323,18 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1340,51 +1344,47 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1392,14 +1392,18 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1409,7 +1413,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1428,13 +1432,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1444,7 +1448,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1463,13 +1467,13 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1498,13 +1502,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1533,13 +1537,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1549,7 +1553,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1563,18 +1567,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1598,19 +1598,19 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1620,58 +1620,58 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1695,14 +1695,18 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1712,7 +1716,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1731,18 +1735,18 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1752,51 +1756,47 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1804,14 +1804,18 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1840,13 +1844,13 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1856,7 +1860,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1875,13 +1879,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1910,13 +1914,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1945,13 +1949,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1961,59 +1965,59 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Biodiversity gain exemption</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain exemption</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2021,12 +2025,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2038,17 +2042,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2056,12 +2060,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2071,19 +2075,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2091,17 +2087,17 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2106,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2118,7 +2114,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2133,11 +2129,19 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2145,7 +2149,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2155,24 +2159,16 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2180,12 +2176,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2199,7 +2195,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2207,12 +2203,12 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2222,24 +2218,36 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Building element type</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2249,16 +2257,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Building elements[]</t>
@@ -2266,24 +2266,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2297,14 +2297,14 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2328,19 +2328,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2385,19 +2385,15 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2407,7 +2403,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2416,20 +2412,24 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2439,28 +2439,32 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2470,19 +2474,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2490,7 +2486,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2509,25 +2505,33 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2546,13 +2550,13 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2562,7 +2566,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2581,13 +2585,13 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2616,13 +2620,13 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2651,13 +2655,13 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2681,23 +2685,19 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2711,24 +2711,20 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2742,15 +2738,19 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2774,19 +2774,19 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -2800,29 +2800,25 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2827,7 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2839,12 +2835,12 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -2858,7 +2854,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2866,7 +2862,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2885,7 +2881,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2893,7 +2889,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2908,11 +2904,19 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Parking arrangements</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Existing parking affected</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2920,34 +2924,26 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Will the proposed works affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Parking arrangements</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Existing parking affected</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2955,26 +2951,34 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Will the proposed works affect existing car parking arrangements</t>
+          <t>A description of how the proposed works will affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2982,34 +2986,26 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>A description of how the proposed works will affect existing car parking arrangements</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3017,17 +3013,17 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3032,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3044,7 +3040,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3063,7 +3059,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3071,7 +3067,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3090,7 +3086,7 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3098,7 +3094,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3113,11 +3109,19 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3125,7 +3129,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3135,24 +3139,16 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3160,12 +3156,12 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3179,7 +3175,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3187,17 +3183,17 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3202,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3214,17 +3210,17 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3229,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3241,39 +3237,51 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3283,16 +3291,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3300,19 +3300,19 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -3362,19 +3362,19 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -3393,14 +3393,14 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -3424,14 +3424,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -3455,14 +3455,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -3486,19 +3486,19 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3539,50 +3539,46 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3590,12 +3586,12 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3609,7 +3605,7 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3617,17 +3613,17 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3636,15 +3632,19 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -3721,28 +3721,32 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Falling trees risk</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -3752,32 +3756,28 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Falling trees risk</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>Falling trees document</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3791,24 +3791,20 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Falling trees document</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Tree removal</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether trees or hedges need to be pruned or removed</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -3822,54 +3818,27 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Tree removal</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>Tree removal plan</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges need to be pruned or removed</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Tree removal plan</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>A unique reference for the data item</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3877,42 +3846,42 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B88:B96"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A61:A75"/>
-    <mergeCell ref="B61:B75"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="A83:A87"/>
-    <mergeCell ref="B47"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="B53:B59"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B96:B101"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B87:B95"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B60:B74"/>
+    <mergeCell ref="B47:B49"/>
     <mergeCell ref="B46"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="A54:A60"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A27:A34"/>
     <mergeCell ref="A46"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A97:A102"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A88:A96"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A35"/>
-    <mergeCell ref="A47"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="A96:A101"/>
+    <mergeCell ref="A87:A95"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="B35:B38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/householder-planning-application-hh.xlsx
+++ b/generated/spreadsheet/householder-planning-application-hh.xlsx
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">

--- a/generated/spreadsheet/householder-planning-application-hh.xlsx
+++ b/generated/spreadsheet/householder-planning-application-hh.xlsx
@@ -433,7 +433,7 @@
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
@@ -2230,24 +2230,20 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2266,24 +2262,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2297,14 +2293,14 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2328,19 +2324,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">

--- a/generated/spreadsheet/householder-planning-application-hh.xlsx
+++ b/generated/spreadsheet/householder-planning-application-hh.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,67 +1063,75 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1135,7 +1139,7 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1154,7 +1158,7 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1162,7 +1166,7 @@
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1181,24 +1185,20 @@
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Change to right of way</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1208,27 +1208,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1243,23 +1239,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1283,18 +1283,14 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1304,7 +1300,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1323,18 +1319,18 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1344,47 +1340,51 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1392,18 +1392,14 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1413,7 +1409,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1432,13 +1428,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1448,7 +1444,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1463,13 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1502,13 +1498,13 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1537,13 +1533,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1553,7 +1549,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1563,18 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1598,19 +1598,19 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1620,58 +1620,58 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1695,18 +1695,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1716,7 +1712,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1735,18 +1731,18 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1756,47 +1752,51 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1804,18 +1804,14 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1825,7 +1821,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1844,13 +1840,13 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1860,7 +1856,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1875,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1914,13 +1910,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1949,13 +1945,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1965,59 +1961,59 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain exemption</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Biodiversity net gain</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Biodiversity gain exemption</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,12 +2021,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2042,17 +2038,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2060,12 +2056,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2075,11 +2071,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2087,17 +2091,17 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2110,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2114,7 +2118,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2129,19 +2133,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2149,7 +2145,7 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2159,16 +2155,24 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2176,12 +2180,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2195,7 +2199,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2203,12 +2207,12 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2218,19 +2222,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2238,12 +2234,12 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2253,28 +2249,32 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2293,24 +2293,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2324,14 +2324,14 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2355,19 +2355,19 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2381,15 +2381,19 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2399,7 +2403,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2408,24 +2412,20 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2435,32 +2435,28 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2470,11 +2466,19 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2482,7 +2486,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2501,33 +2505,25 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2546,13 +2542,13 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -2562,7 +2558,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2581,13 +2577,13 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2616,13 +2612,13 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2651,13 +2647,13 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2667,7 +2663,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2681,19 +2677,23 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -2707,20 +2707,24 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -2734,29 +2738,25 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2765,29 +2765,25 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2796,25 +2792,29 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2823,25 +2823,29 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2854,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2858,7 +2862,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2868,7 +2872,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2881,7 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2885,34 +2889,26 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Parking arrangements</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Existing parking affected</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2920,12 +2916,12 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Will the proposed works affect existing car parking arrangements</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2935,11 +2931,19 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Parking arrangements</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Existing parking affected</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2947,34 +2951,26 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>A description of how the proposed works will affect existing car parking arrangements</t>
+          <t>Will the proposed works affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2982,26 +2978,34 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>A description of how the proposed works will affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3009,17 +3013,17 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3032,7 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3036,7 +3040,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -3055,7 +3059,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3063,12 +3067,12 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -3082,7 +3086,7 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3090,12 +3094,12 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3105,19 +3109,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3125,7 +3121,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3135,16 +3131,24 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="n"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3152,12 +3156,12 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3171,7 +3175,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3179,17 +3183,17 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3202,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3206,17 +3210,17 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3229,7 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3233,51 +3237,39 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3287,8 +3279,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3296,19 +3296,19 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3327,14 +3327,14 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -3358,19 +3358,19 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -3389,19 +3389,19 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -3420,19 +3420,19 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -3451,19 +3451,19 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -3482,19 +3482,19 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3513,14 +3513,14 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3535,46 +3535,50 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3582,12 +3586,12 @@
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -3601,7 +3605,7 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3609,17 +3613,17 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3628,19 +3632,15 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -3695,14 +3695,14 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -3717,32 +3717,28 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Falling trees risk</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -3752,28 +3748,32 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Falling trees document</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Falling trees risk</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3787,20 +3787,24 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tree removal</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+          <t>Falling trees document</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges need to be pruned or removed</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -3814,27 +3818,54 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Tree removal plan</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Tree removal</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
+          <t>Whether trees or hedges need to be pruned or removed</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Tree removal plan</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
           <t>A unique reference for the data item</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3842,42 +3873,42 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="B53:B59"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B96:B101"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B87:B95"/>
-    <mergeCell ref="B39:B44"/>
-    <mergeCell ref="B60:B74"/>
-    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B97:B102"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B88:B96"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="A61:A75"/>
+    <mergeCell ref="B61:B75"/>
+    <mergeCell ref="B83:B87"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="B47"/>
     <mergeCell ref="B46"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="A45"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="B54:B60"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B24:B27"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="A54:A60"/>
     <mergeCell ref="A46"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="A96:A101"/>
-    <mergeCell ref="A87:A95"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="B35:B38"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="A97:A102"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="A78:A82"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A88:A96"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A35"/>
+    <mergeCell ref="A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/householder-planning-application-hh.xlsx
+++ b/generated/spreadsheet/householder-planning-application-hh.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1533,13 +1533,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1568,13 +1572,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1598,14 +1606,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1629,19 +1645,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1651,58 +1667,58 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1726,18 +1742,14 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1747,7 +1759,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1766,18 +1778,18 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -1787,47 +1799,51 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1835,18 +1851,14 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1875,13 +1887,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1891,7 +1903,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1910,13 +1922,13 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1945,13 +1957,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1980,83 +1992,95 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity gain exemption</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2066,24 +2090,24 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Biodiversity net gain</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Biodiversity gain exemption</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2091,7 +2115,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Statement whether the biodiversity gain condition will apply if permission is granted. Householder applicants need to confirm the biodiversity gain condition does not apply.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2106,11 +2130,19 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2118,7 +2150,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2128,16 +2160,24 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2145,31 +2185,23 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Person reference</t>
@@ -2180,7 +2212,7 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2190,7 +2222,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2231,7 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2207,26 +2239,34 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2234,12 +2274,12 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2249,19 +2289,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2269,7 +2301,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2288,24 +2320,20 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2315,33 +2343,37 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>What materials are being used for the proposed development</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2355,24 +2387,24 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2386,19 +2418,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2412,25 +2444,29 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2439,46 +2475,38 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2486,7 +2514,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2505,20 +2533,24 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2528,37 +2560,37 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2567,28 +2599,20 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2612,13 +2636,13 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -2628,7 +2652,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2647,13 +2671,13 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2682,13 +2706,13 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -2698,7 +2722,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2712,24 +2736,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2738,20 +2770,32 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2765,15 +2809,27 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2792,29 +2848,29 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2823,29 +2879,25 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2906,7 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2862,7 +2914,7 @@
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -2872,7 +2924,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2881,20 +2933,24 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -2908,15 +2964,19 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -2931,19 +2991,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Parking arrangements</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Details of any changes the proposed development would make to parking facilities.</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Existing parking affected</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2951,12 +3003,12 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Will the proposed works affect existing car parking arrangements</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -2970,7 +3022,7 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2978,34 +3030,26 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>A description of how the proposed works will affect existing car parking arrangements</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -3013,12 +3057,12 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3028,11 +3072,19 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="2" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Parking arrangements</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Details of any changes the proposed development would make to parking facilities.</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Existing parking affected</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -3040,17 +3092,17 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Will the proposed works affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3111,7 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -3067,7 +3119,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A description of how the proposed works will affect existing car parking arrangements</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3082,11 +3134,19 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="2" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -3094,17 +3154,17 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3173,7 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -3121,7 +3181,7 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -3136,19 +3196,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>What development, works or change of use is proposed</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -3156,7 +3208,7 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -3166,7 +3218,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3227,7 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
@@ -3183,17 +3235,17 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3254,7 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -3210,12 +3262,12 @@
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -3225,11 +3277,19 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>What development, works or change of use is proposed</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -3237,12 +3297,12 @@
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -3256,7 +3316,7 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -3264,51 +3324,39 @@
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Proposal start date</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -3322,29 +3370,25 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3353,24 +3397,20 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -3380,8 +3420,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="2" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3389,24 +3437,24 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3420,24 +3468,28 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3451,19 +3503,23 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -3482,19 +3538,23 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -3513,14 +3573,18 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -3544,19 +3608,19 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -3566,37 +3630,33 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3605,25 +3665,29 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3632,20 +3696,24 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -3655,28 +3723,32 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -3690,24 +3762,20 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -3721,19 +3789,15 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -3743,37 +3807,33 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Falling trees risk</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -3787,19 +3847,19 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Falling trees document</t>
+          <t>Other site visit contact</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -3818,20 +3878,24 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Tree removal</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges need to be pruned or removed</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -3841,31 +3905,124 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Tree removal plan</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Falling trees risk</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
+          <t>Whether there are falling trees on-premises or adjacent premises that are a risk to the development</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Falling trees document</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
           <t>A unique reference for the data item</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Tree removal</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Whether trees or hedges need to be pruned or removed</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Tree removal plan</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>A unique reference for the data item</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3873,42 +4030,42 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B97:B102"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B88:B96"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B49"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="B100:B105"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A61:A75"/>
-    <mergeCell ref="B61:B75"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="A83:A87"/>
-    <mergeCell ref="B47"/>
-    <mergeCell ref="B46"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="B28:B36"/>
+    <mergeCell ref="A63:A78"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A48"/>
+    <mergeCell ref="A91:A99"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="A49"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B63:B78"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="B48"/>
+    <mergeCell ref="A28:A36"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="B81:B85"/>
     <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B91:B99"/>
+    <mergeCell ref="A100:A105"/>
     <mergeCell ref="B24:B27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="A54:A60"/>
-    <mergeCell ref="A46"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="A97:A102"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A88:A96"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="B86:B90"/>
     <mergeCell ref="B20:B23"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A35"/>
-    <mergeCell ref="A47"/>
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="A41:A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
